--- a/consultation-dashboard/test-data/sample2_irregular.xlsx
+++ b/consultation-dashboard/test-data/sample2_irregular.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>상담유형</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
@@ -509,6 +514,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>초진</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -537,6 +547,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -560,6 +575,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,6 +605,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -610,6 +635,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -637,6 +667,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>초진</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -663,6 +698,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -688,6 +728,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -713,6 +758,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -738,6 +788,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -763,6 +818,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>재진</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -791,6 +851,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -816,6 +881,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -839,6 +909,11 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>김상담</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>재진</t>
         </is>
       </c>
     </row>
